--- a/exports/trend_1d/TECHM_full_report.xlsx
+++ b/exports/trend_1d/TECHM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>6.21</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42082</v>
+        <v>42083</v>
       </c>
       <c r="H2" t="n">
-        <v>630.9</v>
+        <v>622.4</v>
       </c>
       <c r="I2" t="n">
         <v>629.5685603384489</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.25</v>
+        <v>-2.58</v>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>3.37</v>
       </c>
       <c r="M2" t="n">
         <v>2.14</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42144</v>
+        <v>42145</v>
       </c>
       <c r="H3" t="n">
-        <v>586.6</v>
+        <v>600.7</v>
       </c>
       <c r="I3" t="n">
         <v>593.0669127419681</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K3" t="n">
-        <v>5.75</v>
+        <v>3.49</v>
       </c>
       <c r="L3" t="n">
         <v>1.8</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>9.66</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42150</v>
+        <v>42151</v>
       </c>
       <c r="H4" t="n">
-        <v>586.1</v>
+        <v>498.7</v>
       </c>
       <c r="I4" t="n">
         <v>549.8572611443814</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.43</v>
+        <v>-16.98</v>
       </c>
       <c r="L4" t="n">
-        <v>4.23</v>
+        <v>17.61</v>
       </c>
       <c r="M4" t="n">
-        <v>2.98</v>
+        <v>10.46</v>
       </c>
       <c r="N4" t="n">
-        <v>2.91</v>
+        <v>14.91</v>
       </c>
       <c r="O4" t="n">
         <v>2.4</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>18.86</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H5" t="n">
-        <v>462.4</v>
+        <v>470.5</v>
       </c>
       <c r="I5" t="n">
         <v>465.2423646382126</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K5" t="n">
-        <v>7.28</v>
+        <v>5.65</v>
       </c>
       <c r="L5" t="n">
         <v>5.67</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42241</v>
+        <v>42242</v>
       </c>
       <c r="H6" t="n">
-        <v>478.6</v>
+        <v>458.8</v>
       </c>
       <c r="I6" t="n">
         <v>467.1145123272788</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>1.72</v>
+        <v>-2.49</v>
       </c>
       <c r="L6" t="n">
         <v>5.46</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>17.09</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H7" t="n">
-        <v>409.3</v>
+        <v>415.2</v>
       </c>
       <c r="I7" t="n">
         <v>410.9409613720447</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K7" t="n">
-        <v>10.79</v>
+        <v>9.5</v>
       </c>
       <c r="L7" t="n">
         <v>15.58</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42466</v>
+        <v>42467</v>
       </c>
       <c r="H8" t="n">
-        <v>406.8</v>
+        <v>398.6</v>
       </c>
       <c r="I8" t="n">
         <v>400.3936561051964</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.02</v>
+        <v>-4</v>
       </c>
       <c r="L8" t="n">
         <v>4.53</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>12.1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42514</v>
+        <v>42515</v>
       </c>
       <c r="H9" t="n">
-        <v>432.9</v>
+        <v>479.1</v>
       </c>
       <c r="I9" t="n">
         <v>446.4966646767781</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.609999999999999</v>
+        <v>-20.2</v>
       </c>
       <c r="L9" t="n">
-        <v>12.12</v>
+        <v>21.05</v>
       </c>
       <c r="M9" t="n">
-        <v>1.17</v>
+        <v>4.16</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>10.67</v>
       </c>
       <c r="O9" t="n">
         <v>-2.02</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.75</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42545</v>
+        <v>42548</v>
       </c>
       <c r="H10" t="n">
-        <v>458.6</v>
+        <v>456.2</v>
       </c>
       <c r="I10" t="n">
         <v>457.0738865314871</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.28</v>
+        <v>-4.78</v>
       </c>
       <c r="L10" t="n">
         <v>6.99</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42681</v>
+        <v>42682</v>
       </c>
       <c r="H11" t="n">
-        <v>399</v>
+        <v>407.9</v>
       </c>
       <c r="I11" t="n">
         <v>399.3127579959913</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K11" t="n">
-        <v>12.54</v>
+        <v>10.59</v>
       </c>
       <c r="L11" t="n">
         <v>4.08</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.38</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42765</v>
+        <v>42766</v>
       </c>
       <c r="H12" t="n">
-        <v>424.6</v>
+        <v>406</v>
       </c>
       <c r="I12" t="n">
         <v>415.4138172624257</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K12" t="n">
-        <v>4.09</v>
+        <v>-0.47</v>
       </c>
       <c r="L12" t="n">
         <v>10.59</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>12.54</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42775</v>
+        <v>42776</v>
       </c>
       <c r="H13" t="n">
-        <v>437.4</v>
+        <v>451.7</v>
       </c>
       <c r="I13" t="n">
         <v>449.9773520151955</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.73</v>
+        <v>-11.26</v>
       </c>
       <c r="L13" t="n">
-        <v>8.57</v>
+        <v>12.12</v>
       </c>
       <c r="M13" t="n">
         <v>2.94</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>11.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42821</v>
+        <v>42822</v>
       </c>
       <c r="H14" t="n">
-        <v>421.9</v>
+        <v>409.4</v>
       </c>
       <c r="I14" t="n">
         <v>419.1213210726856</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.6</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>7.77</v>
+        <v>9.59</v>
       </c>
       <c r="M14" t="n">
         <v>2.22</v>
       </c>
       <c r="N14" t="n">
-        <v>2.83</v>
+        <v>2.96</v>
       </c>
       <c r="O14" t="n">
         <v>3.27</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42870</v>
+        <v>42871</v>
       </c>
       <c r="H15" t="n">
-        <v>396.9</v>
+        <v>398</v>
       </c>
       <c r="I15" t="n">
         <v>397.3842812449129</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K15" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="L15" t="n">
         <v>3.74</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.51</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H16" t="n">
-        <v>377.4</v>
+        <v>371.5</v>
       </c>
       <c r="I16" t="n">
         <v>372.09243080683</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.18</v>
+        <v>-6.66</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
+        <v>7.11</v>
       </c>
       <c r="M16" t="n">
         <v>0.47</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>9.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42949</v>
+        <v>42950</v>
       </c>
       <c r="H17" t="n">
-        <v>358</v>
+        <v>362.9</v>
       </c>
       <c r="I17" t="n">
         <v>358.9637455845658</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K17" t="n">
-        <v>3.63</v>
+        <v>2.31</v>
       </c>
       <c r="L17" t="n">
         <v>4.6</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43285</v>
+        <v>43286</v>
       </c>
       <c r="H18" t="n">
-        <v>599.7</v>
+        <v>592.1</v>
       </c>
       <c r="I18" t="n">
         <v>598.8617758337126</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K18" t="n">
-        <v>65.25</v>
+        <v>63.16</v>
       </c>
       <c r="L18" t="n">
         <v>3.78</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>229</v>
+        <v>230</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>12</v>
+      </c>
+      <c r="U18" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.99</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43328</v>
+        <v>43329</v>
       </c>
       <c r="H19" t="n">
-        <v>613.3</v>
+        <v>631.5</v>
       </c>
       <c r="I19" t="n">
         <v>626.1261187375601</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.58</v>
+        <v>-6.65</v>
       </c>
       <c r="L19" t="n">
-        <v>6.62</v>
+        <v>7.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.18</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>10.83</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43378</v>
+        <v>43381</v>
       </c>
       <c r="H20" t="n">
-        <v>657.1</v>
+        <v>638.3</v>
       </c>
       <c r="I20" t="n">
         <v>646.9007229986781</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K20" t="n">
-        <v>4.05</v>
+        <v>1.08</v>
       </c>
       <c r="L20" t="n">
         <v>4.29</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>14.41</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43403</v>
+        <v>43404</v>
       </c>
       <c r="H21" t="n">
-        <v>629</v>
+        <v>685.3</v>
       </c>
       <c r="I21" t="n">
         <v>664.1241935670372</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>1.46</v>
+        <v>-7.36</v>
       </c>
       <c r="L21" t="n">
-        <v>6.02</v>
+        <v>8.1</v>
       </c>
       <c r="M21" t="n">
         <v>1.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O21" t="n">
         <v>-2.86</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>17.45</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43549</v>
+        <v>43550</v>
       </c>
       <c r="H22" t="n">
-        <v>729</v>
+        <v>710.9</v>
       </c>
       <c r="I22" t="n">
         <v>719.4200539240009</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K22" t="n">
-        <v>6.38</v>
+        <v>3.74</v>
       </c>
       <c r="L22" t="n">
         <v>10.19</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43580</v>
+        <v>43581</v>
       </c>
       <c r="H23" t="n">
-        <v>754.8</v>
+        <v>761.2</v>
       </c>
       <c r="I23" t="n">
         <v>756.9231105021472</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.18</v>
+        <v>-7.08</v>
       </c>
       <c r="L23" t="n">
         <v>7.58</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.12</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43598</v>
+        <v>43599</v>
       </c>
       <c r="H24" t="n">
-        <v>755.5</v>
+        <v>729.4</v>
       </c>
       <c r="I24" t="n">
         <v>735.8593896171512</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.75</v>
+        <v>-4.18</v>
       </c>
       <c r="L24" t="n">
-        <v>3.02</v>
+        <v>4.61</v>
       </c>
       <c r="M24" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0.85</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43684</v>
+        <v>43685</v>
       </c>
       <c r="H25" t="n">
-        <v>618.8</v>
+        <v>624.3</v>
       </c>
       <c r="I25" t="n">
         <v>621.3377276319437</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K25" t="n">
-        <v>15.16</v>
+        <v>14.41</v>
       </c>
       <c r="L25" t="n">
         <v>3.77</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>9.6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H26" t="n">
-        <v>747.7</v>
+        <v>685.7</v>
       </c>
       <c r="I26" t="n">
         <v>736.2973105037848</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K26" t="n">
-        <v>19.77</v>
+        <v>9.84</v>
       </c>
       <c r="L26" t="n">
         <v>6.78</v>
       </c>
       <c r="M26" t="n">
-        <v>1.45</v>
+        <v>2.47</v>
       </c>
       <c r="N26" t="n">
-        <v>3.8</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>0.89</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>13.13</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43985</v>
+        <v>43986</v>
       </c>
       <c r="H27" t="n">
-        <v>502.7</v>
+        <v>530.4</v>
       </c>
       <c r="I27" t="n">
         <v>523.1385687651602</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K27" t="n">
-        <v>26.69</v>
+        <v>22.65</v>
       </c>
       <c r="L27" t="n">
         <v>8.880000000000001</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>12.51</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43997</v>
+        <v>43998</v>
       </c>
       <c r="H28" t="n">
-        <v>498.5</v>
+        <v>483.6</v>
       </c>
       <c r="I28" t="n">
         <v>487.4915582630748</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.01</v>
+        <v>-8.82</v>
       </c>
       <c r="L28" t="n">
-        <v>6.98</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>4.03</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>14.1</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44022</v>
+        <v>44025</v>
       </c>
       <c r="H29" t="n">
-        <v>517.8</v>
+        <v>547.6</v>
       </c>
       <c r="I29" t="n">
         <v>537.6362025851173</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.07</v>
+        <v>-13.23</v>
       </c>
       <c r="L29" t="n">
-        <v>11.99</v>
+        <v>13.56</v>
       </c>
       <c r="M29" t="n">
         <v>1.56</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>5.76</v>
       </c>
       <c r="O29" t="n">
         <v>-2.99</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H30" t="n">
-        <v>912.1</v>
+        <v>903.6</v>
       </c>
       <c r="I30" t="n">
         <v>909.6806824448029</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K30" t="n">
-        <v>66.56</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="L30" t="n">
         <v>5.17</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>10.99</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44294</v>
+        <v>44295</v>
       </c>
       <c r="H31" t="n">
-        <v>958.1</v>
+        <v>981.1</v>
       </c>
       <c r="I31" t="n">
         <v>959.712254088384</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.03</v>
+        <v>-8.58</v>
       </c>
       <c r="L31" t="n">
-        <v>8.24</v>
+        <v>8.98</v>
       </c>
       <c r="M31" t="n">
         <v>1.86</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>10.74</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44467</v>
+        <v>44468</v>
       </c>
       <c r="H32" t="n">
-        <v>1326.7</v>
+        <v>1308.8</v>
       </c>
       <c r="I32" t="n">
         <v>1325.292860360048</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K32" t="n">
-        <v>35.23</v>
+        <v>33.4</v>
       </c>
       <c r="L32" t="n">
         <v>11.31</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.1</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44487</v>
+        <v>44488</v>
       </c>
       <c r="H33" t="n">
-        <v>1389.5</v>
+        <v>1446.4</v>
       </c>
       <c r="I33" t="n">
         <v>1400.844852385995</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-6.17</v>
+        <v>-10.51</v>
       </c>
       <c r="L33" t="n">
-        <v>6.7</v>
+        <v>12.75</v>
       </c>
       <c r="M33" t="n">
         <v>2.17</v>
       </c>
       <c r="N33" t="n">
-        <v>3.49</v>
+        <v>4.09</v>
       </c>
       <c r="O33" t="n">
         <v>-1.35</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.84</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44578</v>
+        <v>44579</v>
       </c>
       <c r="H34" t="n">
-        <v>1621.9</v>
+        <v>1562.9</v>
       </c>
       <c r="I34" t="n">
         <v>1567.815821706869</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K34" t="n">
-        <v>12.13</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>4.72</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.1</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44628</v>
+        <v>44629</v>
       </c>
       <c r="H35" t="n">
-        <v>1372.5</v>
+        <v>1413.6</v>
       </c>
       <c r="I35" t="n">
         <v>1404.353764413375</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K35" t="n">
-        <v>12.18</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L35" t="n">
         <v>5.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>11.05</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44662</v>
+        <v>44663</v>
       </c>
       <c r="H36" t="n">
-        <v>1360.3</v>
+        <v>1327.6</v>
       </c>
       <c r="I36" t="n">
         <v>1332.102329962131</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.77</v>
+        <v>-6.08</v>
       </c>
       <c r="L36" t="n">
-        <v>4.68</v>
+        <v>6.66</v>
       </c>
       <c r="M36" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="N36" t="n">
         <v>3.01</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.44</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44777</v>
+        <v>44778</v>
       </c>
       <c r="H37" t="n">
-        <v>984</v>
+        <v>986.1</v>
       </c>
       <c r="I37" t="n">
         <v>985.8788577848243</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K37" t="n">
-        <v>25.88</v>
+        <v>25.72</v>
       </c>
       <c r="L37" t="n">
         <v>1.91</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H38" t="n">
-        <v>1012.3</v>
+        <v>964.4</v>
       </c>
       <c r="I38" t="n">
         <v>965.4489178152069</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>2.66</v>
+        <v>-2.2</v>
       </c>
       <c r="L38" t="n">
-        <v>1.47</v>
+        <v>3.98</v>
       </c>
       <c r="M38" t="n">
-        <v>1.59</v>
+        <v>3.74</v>
       </c>
       <c r="N38" t="n">
-        <v>2.36</v>
+        <v>4.73</v>
       </c>
       <c r="O38" t="n">
         <v>0.21</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>8.81</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44812</v>
+        <v>44813</v>
       </c>
       <c r="H39" t="n">
-        <v>1016.2</v>
+        <v>1051.6</v>
       </c>
       <c r="I39" t="n">
         <v>1049.391994717369</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.37</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>5.69</v>
+        <v>9.6</v>
       </c>
       <c r="M39" t="n">
         <v>1.38</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H40" t="n">
-        <v>1009.9</v>
+        <v>962.2</v>
       </c>
       <c r="I40" t="n">
         <v>991.0395595897604</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.97</v>
+        <v>-8.5</v>
       </c>
       <c r="L40" t="n">
-        <v>4.42</v>
+        <v>8.98</v>
       </c>
       <c r="M40" t="n">
         <v>3.18</v>
       </c>
       <c r="N40" t="n">
-        <v>2.93</v>
+        <v>4.72</v>
       </c>
       <c r="O40" t="n">
         <v>3.48</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.48</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44895</v>
+        <v>44896</v>
       </c>
       <c r="H41" t="n">
-        <v>1004.1</v>
+        <v>1027.5</v>
       </c>
       <c r="I41" t="n">
         <v>1020.113668163523</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.35</v>
+        <v>-6.79</v>
       </c>
       <c r="L41" t="n">
-        <v>6.52</v>
+        <v>7.43</v>
       </c>
       <c r="M41" t="n">
         <v>2.81</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.67</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H42" t="n">
-        <v>1001.4</v>
+        <v>964.1</v>
       </c>
       <c r="I42" t="n">
         <v>970.4814666530981</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.54</v>
+        <v>-6.17</v>
       </c>
       <c r="L42" t="n">
-        <v>2.9</v>
+        <v>6.64</v>
       </c>
       <c r="M42" t="n">
         <v>0.99</v>
       </c>
       <c r="N42" t="n">
-        <v>1.38</v>
+        <v>3.72</v>
       </c>
       <c r="O42" t="n">
         <v>2.33</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.56</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44946</v>
+        <v>44949</v>
       </c>
       <c r="H43" t="n">
-        <v>974.9</v>
+        <v>992.9</v>
       </c>
       <c r="I43" t="n">
         <v>985.0451365657273</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.12</v>
+        <v>-2.99</v>
       </c>
       <c r="L43" t="n">
         <v>4.01</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.21</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44956</v>
+        <v>44957</v>
       </c>
       <c r="H44" t="n">
-        <v>964.9</v>
+        <v>944.7</v>
       </c>
       <c r="I44" t="n">
         <v>945.6179412715829</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.82</v>
+        <v>-4.85</v>
       </c>
       <c r="L44" t="n">
-        <v>4.52</v>
+        <v>6.68</v>
       </c>
       <c r="M44" t="n">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O44" t="n">
         <v>1.85</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.82</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44972</v>
+        <v>44973</v>
       </c>
       <c r="H45" t="n">
-        <v>998.7</v>
+        <v>1055.1</v>
       </c>
       <c r="I45" t="n">
         <v>999.1933572813401</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.72</v>
+        <v>-11.69</v>
       </c>
       <c r="L45" t="n">
-        <v>6.09</v>
+        <v>12.78</v>
       </c>
       <c r="M45" t="n">
         <v>0.79</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>10.27</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H46" t="n">
-        <v>1013.5</v>
+        <v>959.1</v>
       </c>
       <c r="I46" t="n">
         <v>972.0019942260741</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.94</v>
+        <v>-9.1</v>
       </c>
       <c r="L46" t="n">
-        <v>8.09</v>
+        <v>11.64</v>
       </c>
       <c r="M46" t="n">
-        <v>2.02</v>
+        <v>4.89</v>
       </c>
       <c r="N46" t="n">
-        <v>3.04</v>
+        <v>5.37</v>
       </c>
       <c r="O46" t="n">
         <v>5.65</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.44</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45064</v>
+        <v>45065</v>
       </c>
       <c r="H47" t="n">
-        <v>977</v>
+        <v>999.4</v>
       </c>
       <c r="I47" t="n">
         <v>996.7896017552832</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.87</v>
+        <v>-4.2</v>
       </c>
       <c r="L47" t="n">
-        <v>4.17</v>
+        <v>4.87</v>
       </c>
       <c r="M47" t="n">
         <v>0.87</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.09</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45131</v>
+        <v>45132</v>
       </c>
       <c r="H48" t="n">
-        <v>1085.3</v>
+        <v>1080.2</v>
       </c>
       <c r="I48" t="n">
         <v>1080.909816561181</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K48" t="n">
-        <v>8.6</v>
+        <v>8.08</v>
       </c>
       <c r="L48" t="n">
         <v>2.21</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45145</v>
+        <v>45146</v>
       </c>
       <c r="H49" t="n">
-        <v>1106.2</v>
+        <v>1127</v>
       </c>
       <c r="I49" t="n">
         <v>1115.813585926909</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.41</v>
+        <v>-4.33</v>
       </c>
       <c r="L49" t="n">
-        <v>3.21</v>
+        <v>4.64</v>
       </c>
       <c r="M49" t="n">
         <v>0.99</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>9.34</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H50" t="n">
-        <v>1206.6</v>
+        <v>1150</v>
       </c>
       <c r="I50" t="n">
         <v>1151.267916145549</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K50" t="n">
-        <v>7.06</v>
+        <v>2.04</v>
       </c>
       <c r="L50" t="n">
         <v>2.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="N50" t="n">
-        <v>1.74</v>
+        <v>4.69</v>
       </c>
       <c r="O50" t="n">
         <v>1.88</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H51" t="n">
-        <v>1096.7</v>
+        <v>1128.7</v>
       </c>
       <c r="I51" t="n">
         <v>1110.699720920167</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K51" t="n">
-        <v>4.63</v>
+        <v>1.85</v>
       </c>
       <c r="L51" t="n">
         <v>3.71</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.53</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="H52" t="n">
-        <v>1204</v>
+        <v>1192.5</v>
       </c>
       <c r="I52" t="n">
         <v>1194.974585619812</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K52" t="n">
-        <v>6.67</v>
+        <v>5.65</v>
       </c>
       <c r="L52" t="n">
         <v>3.37</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.05</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45407</v>
+        <v>45408</v>
       </c>
       <c r="H53" t="n">
-        <v>1112.5</v>
+        <v>1197.2</v>
       </c>
       <c r="I53" t="n">
         <v>1181.658027318717</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K53" t="n">
-        <v>6.71</v>
+        <v>-0.39</v>
       </c>
       <c r="L53" t="n">
-        <v>2.72</v>
+        <v>5.87</v>
       </c>
       <c r="M53" t="n">
-        <v>1.06</v>
+        <v>5.14</v>
       </c>
       <c r="N53" t="n">
-        <v>1.97</v>
+        <v>7.61</v>
       </c>
       <c r="O53" t="n">
         <v>-0.96</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.25</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H54" t="n">
-        <v>1204.6</v>
+        <v>1160.9</v>
       </c>
       <c r="I54" t="n">
         <v>1176.108862253633</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K54" t="n">
-        <v>0.62</v>
+        <v>-3.03</v>
       </c>
       <c r="L54" t="n">
-        <v>3.02</v>
+        <v>3.47</v>
       </c>
       <c r="M54" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="N54" t="n">
-        <v>2.22</v>
+        <v>3.63</v>
       </c>
       <c r="O54" t="n">
         <v>7.61</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>8.74</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45449</v>
+        <v>45450</v>
       </c>
       <c r="H55" t="n">
-        <v>1234.2</v>
+        <v>1291.8</v>
       </c>
       <c r="I55" t="n">
         <v>1237.105959330904</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.31</v>
+        <v>-11.28</v>
       </c>
       <c r="L55" t="n">
-        <v>6.83</v>
+        <v>11.55</v>
       </c>
       <c r="M55" t="n">
         <v>2.22</v>
       </c>
       <c r="N55" t="n">
-        <v>4.07</v>
+        <v>4.67</v>
       </c>
       <c r="O55" t="n">
         <v>-3.63</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.39</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="H56" t="n">
-        <v>1614.1</v>
+        <v>1599.6</v>
       </c>
       <c r="I56" t="n">
         <v>1607.196739045156</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K56" t="n">
-        <v>24.95</v>
+        <v>23.83</v>
       </c>
       <c r="L56" t="n">
         <v>3.75</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>8</v>
+      </c>
+      <c r="U56" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>8.08</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="H57" t="n">
-        <v>1317.6</v>
+        <v>1378</v>
       </c>
       <c r="I57" t="n">
         <v>1336.139276031099</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K57" t="n">
-        <v>17.63</v>
+        <v>13.85</v>
       </c>
       <c r="L57" t="n">
         <v>3.9</v>
       </c>
       <c r="M57" t="n">
-        <v>2.49</v>
+        <v>3.07</v>
       </c>
       <c r="N57" t="n">
         <v>5.1</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.01</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="H58" t="n">
-        <v>1561.9</v>
+        <v>1536.8</v>
       </c>
       <c r="I58" t="n">
         <v>1538.561475176299</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K58" t="n">
-        <v>13.35</v>
+        <v>11.52</v>
       </c>
       <c r="L58" t="n">
         <v>4.49</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.28</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H59" t="n">
-        <v>1492.7</v>
+        <v>1508</v>
       </c>
       <c r="I59" t="n">
         <v>1497.010775902774</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K59" t="n">
-        <v>2.87</v>
+        <v>1.87</v>
       </c>
       <c r="L59" t="n">
         <v>2.17</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H60" t="n">
-        <v>1434.6</v>
+        <v>1415.6</v>
       </c>
       <c r="I60" t="n">
         <v>1434.561310665772</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.87</v>
+        <v>-6.13</v>
       </c>
       <c r="L60" t="n">
-        <v>6.07</v>
+        <v>6.99</v>
       </c>
       <c r="M60" t="n">
         <v>3.53</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.28</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H61" t="n">
-        <v>1424.5</v>
+        <v>1456.8</v>
       </c>
       <c r="I61" t="n">
         <v>1425.271999632157</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.63</v>
+        <v>-2.91</v>
       </c>
       <c r="L61" t="n">
-        <v>2.42</v>
+        <v>4.23</v>
       </c>
       <c r="M61" t="n">
         <v>1.13</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.3</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="H62" t="n">
-        <v>1604.5</v>
+        <v>1578.9</v>
       </c>
       <c r="I62" t="n">
         <v>1602.562177206848</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K62" t="n">
-        <v>10.14</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L62" t="n">
         <v>2.2</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>4</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H63" t="n">
-        <v>1412.8</v>
+        <v>1436.1</v>
       </c>
       <c r="I63" t="n">
         <v>1415.112501118958</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K63" t="n">
-        <v>10.52</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L63" t="n">
         <v>2.38</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>10.47</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H64" t="n">
-        <v>1385.5</v>
+        <v>1324.1</v>
       </c>
       <c r="I64" t="n">
         <v>1353.89489075996</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.52</v>
+        <v>-7.8</v>
       </c>
       <c r="L64" t="n">
-        <v>4.71</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>2.5</v>
       </c>
       <c r="N64" t="n">
-        <v>2.81</v>
+        <v>4.43</v>
       </c>
       <c r="O64" t="n">
         <v>1.65</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,25 +4904,25 @@
         <v>13.19</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="H65" t="n">
-        <v>1418.7</v>
+        <v>1446.3</v>
       </c>
       <c r="I65" t="n">
         <v>1436.567761700152</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.14</v>
+        <v>-9.23</v>
       </c>
       <c r="L65" t="n">
         <v>10.91</v>
       </c>
       <c r="M65" t="n">
-        <v>1.14</v>
+        <v>1.47</v>
       </c>
       <c r="N65" t="n">
         <v>4.34</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>8.44</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="H66" t="n">
-        <v>1428</v>
+        <v>1393</v>
       </c>
       <c r="I66" t="n">
         <v>1403.133115064941</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.27</v>
+        <v>-3.69</v>
       </c>
       <c r="L66" t="n">
-        <v>3.11</v>
+        <v>3.97</v>
       </c>
       <c r="M66" t="n">
         <v>1.49</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>11.61</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="H67" t="n">
-        <v>1454.8</v>
+        <v>1504.5</v>
       </c>
       <c r="I67" t="n">
         <v>1474.083373838909</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.44</v>
+        <v>-8</v>
       </c>
       <c r="L67" t="n">
-        <v>6.17</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M67" t="n">
         <v>1.52</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>10.99</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H68" t="n">
-        <v>1559</v>
+        <v>1508</v>
       </c>
       <c r="I68" t="n">
         <v>1532.2381729114</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K68" t="n">
-        <v>3.62</v>
+        <v>0.23</v>
       </c>
       <c r="L68" t="n">
         <v>4.01</v>
@@ -4317,7 +5132,7 @@
         <v>2.94</v>
       </c>
       <c r="N68" t="n">
-        <v>2.06</v>
+        <v>3.27</v>
       </c>
       <c r="O68" t="n">
         <v>3.42</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>8.17</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H69" t="n">
-        <v>1575.2</v>
+        <v>1650</v>
       </c>
       <c r="I69" t="n">
         <v>1597.119444082418</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.46</v>
+        <v>-9.42</v>
       </c>
       <c r="L69" t="n">
-        <v>8.300000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="M69" t="n">
         <v>3.05</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,14 @@
       <c r="Q70" t="n">
         <v>9</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9392,7 +10239,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.8</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="6">
@@ -9402,7 +10249,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -9412,7 +10259,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8">
@@ -9422,7 +10269,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9432,7 +10279,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -9442,7 +10289,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136.6</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="11">
@@ -9452,7 +10299,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -9462,7 +10309,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -9472,7 +10319,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.8</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="14">
@@ -9482,7 +10329,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.64</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="15">
@@ -9492,7 +10339,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.99</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="16">
@@ -9502,7 +10349,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.28</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -9512,7 +10359,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.56</v>
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -9522,7 +10369,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="19">
@@ -9532,7 +10379,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.46</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="20">
@@ -9542,7 +10389,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.64</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="21">
@@ -9552,7 +10399,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.58</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="22">
@@ -9562,7 +10409,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -9572,7 +10419,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -9582,7 +10429,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.11</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="25">
@@ -9592,7 +10439,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.02</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="26">
@@ -9602,7 +10449,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.82</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="27">
@@ -9612,7 +10459,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.24</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="28">
@@ -9622,7 +10469,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
